--- a/output_comparativo_rem_p12/comparativo_rem_p12_mes06_vs_mes12.xlsx
+++ b/output_comparativo_rem_p12/comparativo_rem_p12_mes06_vs_mes12.xlsx
@@ -5201,7 +5201,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>200347</t>
+          <t>109709</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Centro Comunitario de Salud Familiar Alberto Bachelet</t>
+          <t>CECOSF Haydeé Sepúlveda</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5236,65 +5236,65 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>109308</t>
+          <t>109309</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="N39" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O39" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="Q39" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="R39" t="n">
-        <v>9</v>
+        <v>-24</v>
       </c>
       <c r="S39" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="T39" t="n">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="U39" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="V39" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W39" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="X39" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y39" t="n">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="Z39" t="n">
-        <v>412</v>
+        <v>378</v>
       </c>
       <c r="AA39" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="AB39" t="n">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="AC39" t="n">
-        <v>412</v>
+        <v>378</v>
       </c>
       <c r="AD39" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="AE39" t="n">
-        <v>19.42</v>
+        <v>1.34</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>109709</t>
+          <t>200347</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Centro Comunitario de Salud Familiar Dr. José Symón Ojeda</t>
+          <t>Centro Comunitario de Salud Familiar Alberto Bachelet</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5360,65 +5360,65 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>109309</t>
+          <t>109308</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="N40" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="P40" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="Q40" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="R40" t="n">
-        <v>-24</v>
+        <v>9</v>
       </c>
       <c r="S40" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="T40" t="n">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="U40" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="V40" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W40" t="n">
+        <v>60</v>
+      </c>
+      <c r="X40" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>345</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>412</v>
+      </c>
+      <c r="AA40" t="n">
         <v>67</v>
       </c>
-      <c r="X40" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>373</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>378</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>5</v>
-      </c>
       <c r="AB40" t="n">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="AC40" t="n">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="AD40" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.34</v>
+        <v>19.42</v>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Hospital de Til Til</t>
+          <t>Hospital Comunitario de Til Til</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Centro Comunitario de Salud Familiar Lo Chacón</t>
+          <t>CECOSF Wilma Yoli Gomez Conejera</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>Vigente en Operación Habitual</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -21048,7 +21048,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Centro de Salud Familiar Maipo</t>
+          <t>Centro de Salud Familiar Dragica Ciudad Pap</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38378,7 +38378,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>Vigente en Operación Habitual</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
